--- a/tools/打字練習.xlsx
+++ b/tools/打字練習.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7655E971-8E55-4575-9056-0A925F261474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CEF672-26DA-4593-8044-6237A605B035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C92AE23C-EA0B-4853-9724-1F7DCE8D1D5D}"/>
   </bookViews>
   <sheets>
-    <sheet name="漢字注音" sheetId="1" r:id="rId1"/>
+    <sheet name="打字練習表" sheetId="2" r:id="rId1"/>
+    <sheet name="漢字注音" sheetId="1" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="覩9">漢字注音!$A$5</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="531">
   <si>
     <t xml:space="preserve">《予阿媽的批》
 吾妻淑柔，展信安康，
@@ -309,10 +310,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>yt8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ciat7</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1301,13 +1298,583 @@
   </si>
   <si>
     <t>φ</t>
+  </si>
+  <si>
+    <t>hoo6</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>a1</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>bbna3</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>e2</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>ggno3</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>ce1</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>siok7</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>zziu2</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>tian3</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>sin5</t>
+  </si>
+  <si>
+    <t>an1</t>
+  </si>
+  <si>
+    <t>kong1</t>
+  </si>
+  <si>
+    <t>sui2</t>
+  </si>
+  <si>
+    <t>gia5</t>
+  </si>
+  <si>
+    <t>lnng6</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>bah7</t>
+  </si>
+  <si>
+    <t>ggin2</t>
+  </si>
+  <si>
+    <t>ggua3</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ciat7</t>
+  </si>
+  <si>
+    <t>bbu2</t>
+  </si>
+  <si>
+    <t>yong6</t>
+  </si>
+  <si>
+    <t>sing1</t>
+  </si>
+  <si>
+    <t>理</t>
+  </si>
+  <si>
+    <t>li3</t>
+  </si>
+  <si>
+    <t>ciong1</t>
+  </si>
+  <si>
+    <t>sun6</t>
+  </si>
+  <si>
+    <t>gnia2</t>
+  </si>
+  <si>
+    <t>zun2</t>
+  </si>
+  <si>
+    <t>zzip8</t>
+  </si>
+  <si>
+    <t>ya6</t>
+  </si>
+  <si>
+    <t>du3</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>gang1</t>
+  </si>
+  <si>
+    <t>siong3</t>
+  </si>
+  <si>
+    <t>bbin2</t>
+  </si>
+  <si>
+    <t>ggueh8</t>
+  </si>
+  <si>
+    <t>ni2</t>
+  </si>
+  <si>
+    <t>zzu2</t>
+  </si>
+  <si>
+    <t>ggiok8</t>
+  </si>
+  <si>
+    <t>tui6</t>
+  </si>
+  <si>
+    <t>lna3</t>
+  </si>
+  <si>
+    <t>cniu6</t>
+  </si>
+  <si>
+    <t>sin1</t>
+  </si>
+  <si>
+    <t>zai6</t>
+  </si>
+  <si>
+    <t>goo5</t>
+  </si>
+  <si>
+    <t>hiong1</t>
+  </si>
+  <si>
+    <t>敢</t>
+  </si>
+  <si>
+    <t>wan3</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>su6</t>
+  </si>
+  <si>
+    <t>gah7</t>
+  </si>
+  <si>
+    <t>lni3</t>
+  </si>
+  <si>
+    <t>ping6</t>
+  </si>
+  <si>
+    <t>gian1</t>
+  </si>
+  <si>
+    <t>gang6</t>
+  </si>
+  <si>
+    <t>hai3</t>
+  </si>
+  <si>
+    <t>bban6</t>
+  </si>
+  <si>
+    <t>sim1</t>
+  </si>
+  <si>
+    <t>diong1</t>
+  </si>
+  <si>
+    <t>liam6</t>
+  </si>
+  <si>
+    <t>bian6</t>
+  </si>
+  <si>
+    <t>bue1</t>
+  </si>
+  <si>
+    <t>gak7</t>
+  </si>
+  <si>
+    <t>yao2</t>
+  </si>
+  <si>
+    <t>wan6</t>
+  </si>
+  <si>
+    <t>bbi2</t>
+  </si>
+  <si>
+    <t>lam2</t>
+  </si>
+  <si>
+    <t>ho2</t>
+  </si>
+  <si>
+    <t>buan6</t>
+  </si>
+  <si>
+    <t>bbok8</t>
+  </si>
+  <si>
+    <t>bbian2</t>
+  </si>
+  <si>
+    <t>hua1</t>
+  </si>
+  <si>
+    <t>sing6</t>
+  </si>
+  <si>
+    <t>kui1</t>
+  </si>
+  <si>
+    <t>親</t>
+  </si>
+  <si>
+    <t>cin1</t>
+  </si>
+  <si>
+    <t>ga1</t>
+  </si>
+  <si>
+    <t>cun1</t>
+  </si>
+  <si>
+    <t>tni1</t>
+  </si>
+  <si>
+    <t>deh7</t>
+  </si>
+  <si>
+    <t>liao3</t>
+  </si>
+  <si>
+    <t>zit8</t>
+  </si>
+  <si>
+    <t>di6</t>
+  </si>
+  <si>
+    <t>bbang6</t>
+  </si>
+  <si>
+    <t>e6</t>
+  </si>
+  <si>
+    <t>pni1</t>
+  </si>
+  <si>
+    <t>dioh8</t>
+  </si>
+  <si>
+    <t>hue1</t>
+  </si>
+  <si>
+    <t>pang1</t>
+  </si>
+  <si>
+    <t>gin6</t>
+  </si>
+  <si>
+    <t>lai2</t>
+  </si>
+  <si>
+    <t>提</t>
+  </si>
+  <si>
+    <t>teh8</t>
+  </si>
+  <si>
+    <t>bit1</t>
+  </si>
+  <si>
+    <t>lian6</t>
+  </si>
+  <si>
+    <t>zzi6</t>
+  </si>
+  <si>
+    <t>oh8</t>
+  </si>
+  <si>
+    <t>曉</t>
+  </si>
+  <si>
+    <t>hiao3</t>
+  </si>
+  <si>
+    <t>bbnia2</t>
+  </si>
+  <si>
+    <t>sui1</t>
+  </si>
+  <si>
+    <t>zzian2</t>
+  </si>
+  <si>
+    <t>lo3</t>
+  </si>
+  <si>
+    <t>co3</t>
+  </si>
+  <si>
+    <t>骨</t>
+  </si>
+  <si>
+    <t>gut7</t>
+  </si>
+  <si>
+    <t>lat8</t>
+  </si>
+  <si>
+    <t>soo5</t>
+  </si>
+  <si>
+    <t>zzit8</t>
+  </si>
+  <si>
+    <t>dnia6</t>
+  </si>
+  <si>
+    <t>sing2</t>
+  </si>
+  <si>
+    <t>gong1</t>
+  </si>
+  <si>
+    <t>zua3</t>
+  </si>
+  <si>
+    <t>de3</t>
+  </si>
+  <si>
+    <t>zing2</t>
+  </si>
+  <si>
+    <t>dng2</t>
+  </si>
+  <si>
+    <t>hok8</t>
+  </si>
+  <si>
+    <t>wi2</t>
+  </si>
+  <si>
+    <t>din1</t>
+  </si>
+  <si>
+    <t>diong6</t>
+  </si>
+  <si>
+    <t>hu1</t>
+  </si>
+  <si>
+    <t>漢字</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音節</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>聲</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>韻</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>調</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>oo</t>
+  </si>
+  <si>
+    <t>ue</t>
+  </si>
+  <si>
+    <t>iok</t>
+  </si>
+  <si>
+    <t>iu</t>
+  </si>
+  <si>
+    <t>ian</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>an</t>
+  </si>
+  <si>
+    <t>ong</t>
+  </si>
+  <si>
+    <t>ui</t>
+  </si>
+  <si>
+    <t>ia</t>
+  </si>
+  <si>
+    <t>ng</t>
+  </si>
+  <si>
+    <t>ah</t>
+  </si>
+  <si>
+    <t>ua</t>
+  </si>
+  <si>
+    <t>it</t>
+  </si>
+  <si>
+    <t>iat</t>
+  </si>
+  <si>
+    <t>iong</t>
+  </si>
+  <si>
+    <t>ing</t>
+  </si>
+  <si>
+    <t>un</t>
+  </si>
+  <si>
+    <t>ip</t>
+  </si>
+  <si>
+    <t>ang</t>
+  </si>
+  <si>
+    <t>ueh</t>
+  </si>
+  <si>
+    <t>ai</t>
+  </si>
+  <si>
+    <t>uan</t>
+  </si>
+  <si>
+    <t>im</t>
+  </si>
+  <si>
+    <t>iam</t>
+  </si>
+  <si>
+    <t>ak</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>eh</t>
+  </si>
+  <si>
+    <t>ioh</t>
+  </si>
+  <si>
+    <t>oh</t>
+  </si>
+  <si>
+    <t>ut</t>
+  </si>
+  <si>
+    <t>at</t>
+  </si>
+  <si>
+    <t>bbn</t>
+  </si>
+  <si>
+    <t>gg</t>
+  </si>
+  <si>
+    <t>zz</t>
+  </si>
+  <si>
+    <t>ln</t>
+  </si>
+  <si>
+    <t>bb</t>
+  </si>
+  <si>
+    <t>nia</t>
+  </si>
+  <si>
+    <t>ni</t>
+  </si>
+  <si>
+    <t>niu</t>
+  </si>
+  <si>
+    <t>ao</t>
+  </si>
+  <si>
+    <t>iao</t>
+  </si>
+  <si>
+    <t>noo</t>
+  </si>
+  <si>
+    <t>yit8</t>
+  </si>
+  <si>
+    <t>yit8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32">
+  <fonts count="35">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1529,8 +2096,27 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Cascadia Code Mono"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Noto Serif TC Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color rgb="FF009900"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1540,6 +2126,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1614,7 +2212,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1762,6 +2360,18 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2529,15 +3139,15 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2859,6 +3469,2434 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB35FFD-B9E7-464C-BE62-52523AE2371E}">
+  <dimension ref="B3:I168"/>
+  <sheetFormatPr defaultRowHeight="23.25"/>
+  <cols>
+    <col min="2" max="9" width="10.625" style="49" customWidth="1"/>
+    <col min="10" max="13" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7" ht="30">
+      <c r="B3" s="50" t="s">
+        <v>480</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>481</v>
+      </c>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50" t="s">
+        <v>482</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>483</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="B4" s="49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>343</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>485</v>
+      </c>
+      <c r="G5" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>346</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="G6" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>518</v>
+      </c>
+      <c r="F7" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="G7" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>350</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="G8" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>486</v>
+      </c>
+      <c r="G9" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>354</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>519</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>528</v>
+      </c>
+      <c r="G12" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>356</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="G13" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>358</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>487</v>
+      </c>
+      <c r="G14" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>362</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>520</v>
+      </c>
+      <c r="F15" s="49" t="s">
+        <v>488</v>
+      </c>
+      <c r="G15" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="49" t="s">
+        <v>364</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>365</v>
+      </c>
+      <c r="F17" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="G17" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>366</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F18" s="49" t="s">
+        <v>490</v>
+      </c>
+      <c r="G18" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>367</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>491</v>
+      </c>
+      <c r="G19" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>368</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>361</v>
+      </c>
+      <c r="F20" s="49" t="s">
+        <v>492</v>
+      </c>
+      <c r="G20" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="49" t="s">
+        <v>369</v>
+      </c>
+      <c r="E23" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F23" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="G23" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="F24" s="49" t="s">
+        <v>486</v>
+      </c>
+      <c r="G24" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>370</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F25" s="49" t="s">
+        <v>494</v>
+      </c>
+      <c r="G25" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>371</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="F26" s="49" t="s">
+        <v>495</v>
+      </c>
+      <c r="G26" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>349</v>
+      </c>
+      <c r="F27" s="49" t="s">
+        <v>496</v>
+      </c>
+      <c r="G27" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>374</v>
+      </c>
+      <c r="E28" s="49" t="s">
+        <v>519</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>490</v>
+      </c>
+      <c r="G28" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="49" t="s">
+        <v>375</v>
+      </c>
+      <c r="E30" s="49" t="s">
+        <v>519</v>
+      </c>
+      <c r="F30" s="49" t="s">
+        <v>497</v>
+      </c>
+      <c r="G30" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="B31" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>529</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>376</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>498</v>
+      </c>
+      <c r="G31" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="49" t="s">
+        <v>377</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>499</v>
+      </c>
+      <c r="G32" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="49" t="s">
+        <v>378</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F33" s="49" t="s">
+        <v>353</v>
+      </c>
+      <c r="G33" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="49" t="s">
+        <v>379</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>376</v>
+      </c>
+      <c r="F34" s="49" t="s">
+        <v>492</v>
+      </c>
+      <c r="G34" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="49" t="s">
+        <v>380</v>
+      </c>
+      <c r="E36" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F36" s="49" t="s">
+        <v>501</v>
+      </c>
+      <c r="G36" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="C37" s="49" t="s">
+        <v>382</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G37" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="49" t="s">
+        <v>383</v>
+      </c>
+      <c r="E38" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="F38" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="G38" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="49" t="s">
+        <v>384</v>
+      </c>
+      <c r="E39" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F39" s="49" t="s">
+        <v>502</v>
+      </c>
+      <c r="G39" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="49" t="s">
+        <v>385</v>
+      </c>
+      <c r="E41" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F41" s="49" t="s">
+        <v>523</v>
+      </c>
+      <c r="G41" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="49" t="s">
+        <v>386</v>
+      </c>
+      <c r="E42" s="49" t="s">
+        <v>363</v>
+      </c>
+      <c r="F42" s="49" t="s">
+        <v>502</v>
+      </c>
+      <c r="G42" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="49" t="s">
+        <v>387</v>
+      </c>
+      <c r="E43" s="49" t="s">
+        <v>520</v>
+      </c>
+      <c r="F43" s="49" t="s">
+        <v>503</v>
+      </c>
+      <c r="G43" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>388</v>
+      </c>
+      <c r="E44" s="49" t="s">
+        <v>376</v>
+      </c>
+      <c r="F44" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="G44" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="49" t="s">
+        <v>389</v>
+      </c>
+      <c r="E46" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F46" s="49" t="s">
+        <v>353</v>
+      </c>
+      <c r="G46" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" s="49" t="s">
+        <v>391</v>
+      </c>
+      <c r="E47" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F47" s="49" t="s">
+        <v>504</v>
+      </c>
+      <c r="G47" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="49" t="s">
+        <v>392</v>
+      </c>
+      <c r="E48" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F48" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="G48" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>380</v>
+      </c>
+      <c r="E49" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F49" s="49" t="s">
+        <v>501</v>
+      </c>
+      <c r="G49" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="49" t="s">
+        <v>393</v>
+      </c>
+      <c r="E50" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F50" s="49" t="s">
+        <v>490</v>
+      </c>
+      <c r="G50" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="E51" s="49" t="s">
+        <v>519</v>
+      </c>
+      <c r="F51" s="49" t="s">
+        <v>505</v>
+      </c>
+      <c r="G51" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="49" t="s">
+        <v>395</v>
+      </c>
+      <c r="F53" s="49" t="s">
+        <v>524</v>
+      </c>
+      <c r="G53" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7">
+      <c r="B54" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="49" t="s">
+        <v>396</v>
+      </c>
+      <c r="E54" s="49" t="s">
+        <v>520</v>
+      </c>
+      <c r="F54" s="49" t="s">
+        <v>353</v>
+      </c>
+      <c r="G54" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7">
+      <c r="B55" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="49" t="s">
+        <v>397</v>
+      </c>
+      <c r="E55" s="49" t="s">
+        <v>519</v>
+      </c>
+      <c r="F55" s="49" t="s">
+        <v>487</v>
+      </c>
+      <c r="G55" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" s="49" t="s">
+        <v>398</v>
+      </c>
+      <c r="E56" s="49" t="s">
+        <v>365</v>
+      </c>
+      <c r="F56" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="G56" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7">
+      <c r="B58" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="49" t="s">
+        <v>399</v>
+      </c>
+      <c r="E58" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="F58" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="G58" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7">
+      <c r="B59" s="49" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59" s="49" t="s">
+        <v>400</v>
+      </c>
+      <c r="E59" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="F59" s="49" t="s">
+        <v>525</v>
+      </c>
+      <c r="G59" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7">
+      <c r="B60" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" s="49" t="s">
+        <v>401</v>
+      </c>
+      <c r="E60" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F60" s="49" t="s">
+        <v>490</v>
+      </c>
+      <c r="G60" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="B61" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="49" t="s">
+        <v>402</v>
+      </c>
+      <c r="E61" s="49" t="s">
+        <v>363</v>
+      </c>
+      <c r="F61" s="49" t="s">
+        <v>506</v>
+      </c>
+      <c r="G61" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7">
+      <c r="B62" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="49" t="s">
+        <v>403</v>
+      </c>
+      <c r="E62" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F62" s="49" t="s">
+        <v>485</v>
+      </c>
+      <c r="G62" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7">
+      <c r="B63" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" s="49" t="s">
+        <v>404</v>
+      </c>
+      <c r="E63" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F63" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="G63" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7">
+      <c r="B64" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7">
+      <c r="B65" s="49" t="s">
+        <v>405</v>
+      </c>
+      <c r="C65" s="49" t="s">
+        <v>406</v>
+      </c>
+      <c r="E65" s="49" t="s">
+        <v>407</v>
+      </c>
+      <c r="F65" s="49" t="s">
+        <v>491</v>
+      </c>
+      <c r="G65" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7">
+      <c r="B66" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="C66" s="49" t="s">
+        <v>408</v>
+      </c>
+      <c r="E66" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F66" s="49" t="s">
+        <v>353</v>
+      </c>
+      <c r="G66" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7">
+      <c r="B67" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>409</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F67" s="49" t="s">
+        <v>496</v>
+      </c>
+      <c r="G67" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7">
+      <c r="B68" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C68" s="49" t="s">
+        <v>410</v>
+      </c>
+      <c r="E68" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="F68" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G68" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7">
+      <c r="B69" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" s="49" t="s">
+        <v>411</v>
+      </c>
+      <c r="E69" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="F69" s="49" t="s">
+        <v>501</v>
+      </c>
+      <c r="G69" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7">
+      <c r="B70" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="49" t="s">
+        <v>412</v>
+      </c>
+      <c r="E70" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F70" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="G70" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7">
+      <c r="B71" s="49" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" s="49" t="s">
+        <v>413</v>
+      </c>
+      <c r="E71" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F71" s="49" t="s">
+        <v>504</v>
+      </c>
+      <c r="G71" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7">
+      <c r="B72" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="C72" s="49" t="s">
+        <v>392</v>
+      </c>
+      <c r="E72" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F72" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="G72" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7">
+      <c r="B73" s="49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7">
+      <c r="B74" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" s="49" t="s">
+        <v>391</v>
+      </c>
+      <c r="E74" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F74" s="49" t="s">
+        <v>504</v>
+      </c>
+      <c r="G74" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7">
+      <c r="B75" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C75" s="49" t="s">
+        <v>414</v>
+      </c>
+      <c r="E75" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F75" s="49" t="s">
+        <v>506</v>
+      </c>
+      <c r="G75" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7">
+      <c r="B76" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="C76" s="49" t="s">
+        <v>415</v>
+      </c>
+      <c r="E76" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F76" s="49" t="s">
+        <v>491</v>
+      </c>
+      <c r="G76" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7">
+      <c r="B77" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="C77" s="49" t="s">
+        <v>382</v>
+      </c>
+      <c r="E77" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F77" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G77" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7">
+      <c r="B78" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7">
+      <c r="B79" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C79" s="49" t="s">
+        <v>416</v>
+      </c>
+      <c r="E79" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F79" s="49" t="s">
+        <v>508</v>
+      </c>
+      <c r="G79" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7">
+      <c r="B80" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="C80" s="49" t="s">
+        <v>417</v>
+      </c>
+      <c r="E80" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F80" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="G80" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7">
+      <c r="B81" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="E81" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F81" s="49" t="s">
+        <v>509</v>
+      </c>
+      <c r="G81" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7">
+      <c r="B82" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C82" s="49" t="s">
+        <v>410</v>
+      </c>
+      <c r="E82" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="F82" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G82" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7">
+      <c r="B83" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7">
+      <c r="B84" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="C84" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="E84" s="49" t="s">
+        <v>349</v>
+      </c>
+      <c r="F84" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="G84" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7">
+      <c r="B85" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="49" t="s">
+        <v>420</v>
+      </c>
+      <c r="E85" s="49" t="s">
+        <v>349</v>
+      </c>
+      <c r="F85" s="49" t="s">
+        <v>486</v>
+      </c>
+      <c r="G85" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7">
+      <c r="B86" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="C86" s="49" t="s">
+        <v>421</v>
+      </c>
+      <c r="E86" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F86" s="49" t="s">
+        <v>510</v>
+      </c>
+      <c r="G86" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7">
+      <c r="B87" s="49" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="49" t="s">
+        <v>422</v>
+      </c>
+      <c r="E87" s="49" t="s">
+        <v>376</v>
+      </c>
+      <c r="F87" s="49" t="s">
+        <v>526</v>
+      </c>
+      <c r="G87" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7">
+      <c r="B88" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" s="49" t="s">
+        <v>423</v>
+      </c>
+      <c r="E88" s="49" t="s">
+        <v>407</v>
+      </c>
+      <c r="F88" s="49" t="s">
+        <v>491</v>
+      </c>
+      <c r="G88" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7">
+      <c r="B89" s="49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7">
+      <c r="B90" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="C90" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="E90" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F90" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G90" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7">
+      <c r="B91" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C91" s="49" t="s">
+        <v>425</v>
+      </c>
+      <c r="E91" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F91" s="49" t="s">
+        <v>511</v>
+      </c>
+      <c r="G91" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7">
+      <c r="B92" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="C92" s="49" t="s">
+        <v>426</v>
+      </c>
+      <c r="E92" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F92" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="G92" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7">
+      <c r="B93" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="C93" s="49" t="s">
+        <v>427</v>
+      </c>
+      <c r="E93" s="49" t="s">
+        <v>349</v>
+      </c>
+      <c r="F93" s="49" t="s">
+        <v>507</v>
+      </c>
+      <c r="G93" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7">
+      <c r="B94" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="C94" s="49" t="s">
+        <v>428</v>
+      </c>
+      <c r="E94" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F94" s="49" t="s">
+        <v>512</v>
+      </c>
+      <c r="G94" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7">
+      <c r="B95" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="C95" s="49" t="s">
+        <v>429</v>
+      </c>
+      <c r="E95" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F95" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="G95" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7">
+      <c r="B96" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="C96" s="49" t="s">
+        <v>430</v>
+      </c>
+      <c r="E96" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F96" s="49" t="s">
+        <v>497</v>
+      </c>
+      <c r="G96" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7">
+      <c r="B97" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="C97" s="49" t="s">
+        <v>431</v>
+      </c>
+      <c r="E97" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F97" s="49" t="s">
+        <v>501</v>
+      </c>
+      <c r="G97" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7">
+      <c r="B98" s="49" t="s">
+        <v>227</v>
+      </c>
+      <c r="C98" s="49" t="s">
+        <v>432</v>
+      </c>
+      <c r="E98" s="49" t="s">
+        <v>361</v>
+      </c>
+      <c r="F98" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="G98" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7">
+      <c r="B99" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7">
+      <c r="B100" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="C100" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="E100" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="F100" s="49" t="s">
+        <v>490</v>
+      </c>
+      <c r="G100" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7">
+      <c r="B101" s="49" t="s">
+        <v>229</v>
+      </c>
+      <c r="C101" s="49" t="s">
+        <v>400</v>
+      </c>
+      <c r="E101" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="F101" s="49" t="s">
+        <v>525</v>
+      </c>
+      <c r="G101" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7">
+      <c r="B102" s="49" t="s">
+        <v>230</v>
+      </c>
+      <c r="C102" s="49" t="s">
+        <v>435</v>
+      </c>
+      <c r="E102" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F102" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="G102" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="B103" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="C103" s="49" t="s">
+        <v>404</v>
+      </c>
+      <c r="E103" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F103" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="G103" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
+      <c r="B104" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="49" t="s">
+        <v>350</v>
+      </c>
+      <c r="F104" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="G104" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7">
+      <c r="B105" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="C105" s="49" t="s">
+        <v>436</v>
+      </c>
+      <c r="E105" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="F105" s="49" t="s">
+        <v>502</v>
+      </c>
+      <c r="G105" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7">
+      <c r="B106" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="C106" s="49" t="s">
+        <v>437</v>
+      </c>
+      <c r="E106" s="49" t="s">
+        <v>365</v>
+      </c>
+      <c r="F106" s="49" t="s">
+        <v>524</v>
+      </c>
+      <c r="G106" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
+      <c r="B107" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="B108" s="49" t="s">
+        <v>233</v>
+      </c>
+      <c r="C108" s="49" t="s">
+        <v>438</v>
+      </c>
+      <c r="E108" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F108" s="49" t="s">
+        <v>513</v>
+      </c>
+      <c r="G108" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7">
+      <c r="B109" s="49" t="s">
+        <v>234</v>
+      </c>
+      <c r="C109" s="49" t="s">
+        <v>439</v>
+      </c>
+      <c r="E109" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F109" s="49" t="s">
+        <v>527</v>
+      </c>
+      <c r="G109" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7">
+      <c r="B110" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C110" s="49" t="s">
+        <v>440</v>
+      </c>
+      <c r="E110" s="49" t="s">
+        <v>363</v>
+      </c>
+      <c r="F110" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="G110" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7">
+      <c r="B111" s="49" t="s">
+        <v>235</v>
+      </c>
+      <c r="C111" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E111" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F111" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="G111" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7">
+      <c r="B112" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C112" s="49" t="s">
+        <v>441</v>
+      </c>
+      <c r="E112" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F112" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G112" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7">
+      <c r="B113" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="E113" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="F113" s="49" t="s">
+        <v>486</v>
+      </c>
+      <c r="G113" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7">
+      <c r="B114" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="C114" s="49" t="s">
+        <v>417</v>
+      </c>
+      <c r="E114" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F114" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="G114" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7">
+      <c r="B115" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7">
+      <c r="B116" s="49" t="s">
+        <v>249</v>
+      </c>
+      <c r="C116" s="49" t="s">
+        <v>442</v>
+      </c>
+      <c r="E116" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F116" s="49" t="s">
+        <v>504</v>
+      </c>
+      <c r="G116" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7">
+      <c r="B117" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C117" s="49" t="s">
+        <v>410</v>
+      </c>
+      <c r="E117" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="F117" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G117" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7">
+      <c r="B118" s="49" t="s">
+        <v>250</v>
+      </c>
+      <c r="C118" s="49" t="s">
+        <v>388</v>
+      </c>
+      <c r="E118" s="49" t="s">
+        <v>376</v>
+      </c>
+      <c r="F118" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="G118" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7">
+      <c r="B119" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="C119" s="49" t="s">
+        <v>443</v>
+      </c>
+      <c r="F119" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="G119" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7">
+      <c r="B120" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="C120" s="49" t="s">
+        <v>444</v>
+      </c>
+      <c r="E120" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="F120" s="49" t="s">
+        <v>524</v>
+      </c>
+      <c r="G120" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7">
+      <c r="B121" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="C121" s="49" t="s">
+        <v>445</v>
+      </c>
+      <c r="E121" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F121" s="49" t="s">
+        <v>514</v>
+      </c>
+      <c r="G121" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7">
+      <c r="B122" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="C122" s="49" t="s">
+        <v>446</v>
+      </c>
+      <c r="E122" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F122" s="49" t="s">
+        <v>486</v>
+      </c>
+      <c r="G122" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7">
+      <c r="B123" s="49" t="s">
+        <v>254</v>
+      </c>
+      <c r="C123" s="49" t="s">
+        <v>447</v>
+      </c>
+      <c r="E123" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="F123" s="49" t="s">
+        <v>504</v>
+      </c>
+      <c r="G123" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7">
+      <c r="B124" s="49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7">
+      <c r="B126" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="C126" s="49" t="s">
+        <v>448</v>
+      </c>
+      <c r="E126" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F126" s="49" t="s">
+        <v>490</v>
+      </c>
+      <c r="G126" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7">
+      <c r="B127" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="C127" s="49" t="s">
+        <v>449</v>
+      </c>
+      <c r="E127" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F127" s="49" t="s">
+        <v>506</v>
+      </c>
+      <c r="G127" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7">
+      <c r="B128" s="49" t="s">
+        <v>450</v>
+      </c>
+      <c r="C128" s="49" t="s">
+        <v>451</v>
+      </c>
+      <c r="E128" s="49" t="s">
+        <v>365</v>
+      </c>
+      <c r="F128" s="49" t="s">
+        <v>513</v>
+      </c>
+      <c r="G128" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7">
+      <c r="B129" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="C129" s="49" t="s">
+        <v>452</v>
+      </c>
+      <c r="E129" s="49" t="s">
+        <v>349</v>
+      </c>
+      <c r="F129" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="G129" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7">
+      <c r="B130" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="C130" s="49" t="s">
+        <v>453</v>
+      </c>
+      <c r="E130" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F130" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="G130" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7">
+      <c r="B131" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="C131" s="49" t="s">
+        <v>454</v>
+      </c>
+      <c r="E131" s="49" t="s">
+        <v>520</v>
+      </c>
+      <c r="F131" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G131" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="2:7">
+      <c r="B132" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7">
+      <c r="B133" s="49" t="s">
+        <v>276</v>
+      </c>
+      <c r="C133" s="49" t="s">
+        <v>455</v>
+      </c>
+      <c r="F133" s="49" t="s">
+        <v>515</v>
+      </c>
+      <c r="G133" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7">
+      <c r="B134" s="49" t="s">
+        <v>277</v>
+      </c>
+      <c r="C134" s="49" t="s">
+        <v>443</v>
+      </c>
+      <c r="F134" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="G134" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="2:7">
+      <c r="B135" s="49" t="s">
+        <v>456</v>
+      </c>
+      <c r="C135" s="49" t="s">
+        <v>457</v>
+      </c>
+      <c r="E135" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F135" s="49" t="s">
+        <v>527</v>
+      </c>
+      <c r="G135" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7">
+      <c r="B136" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C136" s="49" t="s">
+        <v>410</v>
+      </c>
+      <c r="E136" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="F136" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G136" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7">
+      <c r="B137" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" s="49" t="s">
+        <v>350</v>
+      </c>
+      <c r="F137" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="G137" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7">
+      <c r="B138" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="C138" s="49" t="s">
+        <v>458</v>
+      </c>
+      <c r="E138" s="49" t="s">
+        <v>518</v>
+      </c>
+      <c r="F138" s="49" t="s">
+        <v>494</v>
+      </c>
+      <c r="G138" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7">
+      <c r="B139" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="2:7">
+      <c r="B140" s="49" t="s">
+        <v>280</v>
+      </c>
+      <c r="C140" s="49" t="s">
+        <v>459</v>
+      </c>
+      <c r="E140" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F140" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="G140" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="2:7">
+      <c r="B141" s="49" t="s">
+        <v>300</v>
+      </c>
+      <c r="C141" s="49" t="s">
+        <v>460</v>
+      </c>
+      <c r="E141" s="49" t="s">
+        <v>520</v>
+      </c>
+      <c r="F141" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="G141" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="2:7">
+      <c r="B142" s="49" t="s">
+        <v>301</v>
+      </c>
+      <c r="C142" s="49" t="s">
+        <v>461</v>
+      </c>
+      <c r="E142" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F142" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="G142" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="2:7">
+      <c r="B143" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="C143" s="49" t="s">
+        <v>462</v>
+      </c>
+      <c r="E143" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="F143" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="G143" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="2:7">
+      <c r="B144" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7">
+      <c r="B145" s="49" t="s">
+        <v>463</v>
+      </c>
+      <c r="C145" s="49" t="s">
+        <v>464</v>
+      </c>
+      <c r="E145" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F145" s="49" t="s">
+        <v>516</v>
+      </c>
+      <c r="G145" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7">
+      <c r="B146" s="49" t="s">
+        <v>304</v>
+      </c>
+      <c r="C146" s="49" t="s">
+        <v>465</v>
+      </c>
+      <c r="E146" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="F146" s="49" t="s">
+        <v>517</v>
+      </c>
+      <c r="G146" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7">
+      <c r="B147" s="49" t="s">
+        <v>305</v>
+      </c>
+      <c r="C147" s="49" t="s">
+        <v>466</v>
+      </c>
+      <c r="E147" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F147" s="49" t="s">
+        <v>485</v>
+      </c>
+      <c r="G147" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7">
+      <c r="B148" s="49" t="s">
+        <v>306</v>
+      </c>
+      <c r="C148" s="49" t="s">
+        <v>467</v>
+      </c>
+      <c r="E148" s="49" t="s">
+        <v>520</v>
+      </c>
+      <c r="F148" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="G148" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7">
+      <c r="B149" s="49" t="s">
+        <v>307</v>
+      </c>
+      <c r="C149" s="49" t="s">
+        <v>468</v>
+      </c>
+      <c r="E149" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F149" s="49" t="s">
+        <v>523</v>
+      </c>
+      <c r="G149" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7">
+      <c r="B150" s="49" t="s">
+        <v>277</v>
+      </c>
+      <c r="C150" s="49" t="s">
+        <v>443</v>
+      </c>
+      <c r="F150" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="G150" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="2:7">
+      <c r="B151" s="49" t="s">
+        <v>308</v>
+      </c>
+      <c r="C151" s="49" t="s">
+        <v>469</v>
+      </c>
+      <c r="E151" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F151" s="49" t="s">
+        <v>501</v>
+      </c>
+      <c r="G151" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7">
+      <c r="B152" s="49" t="s">
+        <v>309</v>
+      </c>
+      <c r="C152" s="49" t="s">
+        <v>470</v>
+      </c>
+      <c r="E152" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F152" s="49" t="s">
+        <v>492</v>
+      </c>
+      <c r="G152" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7">
+      <c r="B153" s="49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7">
+      <c r="B154" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="C154" s="49" t="s">
+        <v>471</v>
+      </c>
+      <c r="E154" s="49" t="s">
+        <v>363</v>
+      </c>
+      <c r="F154" s="49" t="s">
+        <v>497</v>
+      </c>
+      <c r="G154" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7">
+      <c r="B155" s="49" t="s">
+        <v>311</v>
+      </c>
+      <c r="C155" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="E155" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F155" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="G155" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7">
+      <c r="B156" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="C156" s="49" t="s">
+        <v>473</v>
+      </c>
+      <c r="E156" s="49" t="s">
+        <v>363</v>
+      </c>
+      <c r="F156" s="49" t="s">
+        <v>501</v>
+      </c>
+      <c r="G156" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7">
+      <c r="B157" s="49" t="s">
+        <v>330</v>
+      </c>
+      <c r="C157" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="E157" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F157" s="49" t="s">
+        <v>495</v>
+      </c>
+      <c r="G157" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:7">
+      <c r="B158" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7">
+      <c r="B159" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="C159" s="49" t="s">
+        <v>475</v>
+      </c>
+      <c r="E159" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F159" s="49" t="s">
+        <v>512</v>
+      </c>
+      <c r="G159" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7">
+      <c r="B160" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="C160" s="49" t="s">
+        <v>476</v>
+      </c>
+      <c r="E160" s="49" t="s">
+        <v>407</v>
+      </c>
+      <c r="F160" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="G160" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7">
+      <c r="B161" s="49" t="s">
+        <v>333</v>
+      </c>
+      <c r="C161" s="49" t="s">
+        <v>477</v>
+      </c>
+      <c r="E161" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F161" s="49" t="s">
+        <v>490</v>
+      </c>
+      <c r="G161" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="2:7">
+      <c r="B162" s="49" t="s">
+        <v>334</v>
+      </c>
+      <c r="C162" s="49" t="s">
+        <v>478</v>
+      </c>
+      <c r="E162" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="F162" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="G162" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7">
+      <c r="B163" s="49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7">
+      <c r="B165" s="49" t="s">
+        <v>341</v>
+      </c>
+      <c r="C165" s="49" t="s">
+        <v>479</v>
+      </c>
+      <c r="E165" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F165" s="49" t="s">
+        <v>353</v>
+      </c>
+      <c r="G165" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="2:7">
+      <c r="B166" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="167" spans="2:7">
+      <c r="B167" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="C167" s="49" t="s">
+        <v>428</v>
+      </c>
+      <c r="E167" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F167" s="49" t="s">
+        <v>512</v>
+      </c>
+      <c r="G167" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="2:7">
+      <c r="B168" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="C168" s="49" t="s">
+        <v>380</v>
+      </c>
+      <c r="E168" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="F168" s="49" t="s">
+        <v>501</v>
+      </c>
+      <c r="G168" s="49">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79C6D9FD-E2E2-427E-AE71-0AFDC43AD2B6}">
   <dimension ref="A1:V482"/>
   <sheetFormatPr defaultRowHeight="39"/>
@@ -3397,24 +6435,24 @@
       <c r="K14" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="L14" s="26" t="s">
+      <c r="L14" s="52" t="s">
+        <v>530</v>
+      </c>
+      <c r="M14" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="M14" s="26" t="s">
+      <c r="N14" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="N14" s="26" t="s">
+      <c r="O14" s="26" t="s">
         <v>73</v>
-      </c>
-      <c r="O14" s="26" t="s">
-        <v>74</v>
       </c>
       <c r="P14" s="26"/>
       <c r="Q14" s="26" t="s">
         <v>48</v>
       </c>
       <c r="R14" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S14" s="32"/>
       <c r="V14" s="19"/>
@@ -3426,21 +6464,21 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
       <c r="G15" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
       <c r="L15" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
       <c r="P15" s="12"/>
       <c r="Q15" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R15" s="12"/>
       <c r="V15" s="19"/>
@@ -3448,42 +6486,42 @@
     <row r="16" spans="1:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="16"/>
       <c r="D16" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="17" t="s">
         <v>79</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>80</v>
       </c>
       <c r="F16" s="17"/>
       <c r="G16" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H16" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="J16" s="17" t="s">
         <v>82</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>83</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M16" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>84</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>85</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>48</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R16" s="17"/>
       <c r="S16" s="18"/>
@@ -3495,46 +6533,46 @@
         <v>4</v>
       </c>
       <c r="D17" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="F17" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="G17" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="H17" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="I17" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="J17" s="21" t="s">
         <v>92</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>93</v>
       </c>
       <c r="K17" s="21" t="s">
         <v>29</v>
       </c>
       <c r="L17" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="M17" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="M17" s="21" t="s">
+      <c r="N17" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="N17" s="21" t="s">
+      <c r="O17" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O17" s="21" t="s">
+      <c r="P17" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="P17" s="21" t="s">
+      <c r="Q17" s="21" t="s">
         <v>98</v>
-      </c>
-      <c r="Q17" s="21" t="s">
-        <v>99</v>
       </c>
       <c r="R17" s="21" t="s">
         <v>29</v>
@@ -3545,42 +6583,42 @@
     <row r="18" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="24"/>
       <c r="D18" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F18" s="26"/>
       <c r="G18" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="26" t="s">
+      <c r="I18" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I18" s="26" t="s">
+      <c r="J18" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="J18" s="26" t="s">
-        <v>104</v>
       </c>
       <c r="K18" s="26"/>
       <c r="L18" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="M18" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="M18" s="26" t="s">
+      <c r="N18" s="26" t="s">
         <v>106</v>
-      </c>
-      <c r="N18" s="26" t="s">
-        <v>107</v>
       </c>
       <c r="O18" s="26" t="s">
         <v>48</v>
       </c>
       <c r="P18" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q18" s="26" t="s">
         <v>108</v>
-      </c>
-      <c r="Q18" s="26" t="s">
-        <v>109</v>
       </c>
       <c r="R18" s="26"/>
       <c r="S18" s="32"/>
@@ -3590,78 +6628,78 @@
       <c r="B19" s="10"/>
       <c r="C19" s="36"/>
       <c r="D19" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="J19" s="12" t="s">
         <v>111</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>112</v>
       </c>
       <c r="K19" s="12"/>
       <c r="L19" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
       <c r="O19" s="12"/>
       <c r="P19" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q19" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="Q19" s="12" t="s">
+      <c r="R19" s="12" t="s">
         <v>115</v>
-      </c>
-      <c r="R19" s="12" t="s">
-        <v>116</v>
       </c>
       <c r="V19" s="19"/>
     </row>
     <row r="20" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="16"/>
       <c r="D20" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E20" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="G20" s="17" t="s">
         <v>118</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>119</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="J20" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="J20" s="17" t="s">
+      <c r="K20" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="K20" s="17" t="s">
+      <c r="M20" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="L20" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="M20" s="17" t="s">
+      <c r="N20" s="17" t="s">
         <v>121</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>122</v>
       </c>
       <c r="O20" s="17"/>
       <c r="P20" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q20" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="R20" s="17" t="s">
         <v>123</v>
-      </c>
-      <c r="R20" s="17" t="s">
-        <v>124</v>
       </c>
       <c r="S20" s="18"/>
       <c r="V20" s="19"/>
@@ -3672,49 +6710,49 @@
         <v>5</v>
       </c>
       <c r="D21" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="F21" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="G21" s="21" t="s">
         <v>127</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>128</v>
       </c>
       <c r="H21" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I21" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="J21" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="J21" s="21" t="s">
+      <c r="K21" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="K21" s="21" t="s">
+      <c r="L21" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="L21" s="21" t="s">
+      <c r="M21" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="M21" s="21" t="s">
+      <c r="N21" s="21" t="s">
         <v>133</v>
-      </c>
-      <c r="N21" s="21" t="s">
-        <v>134</v>
       </c>
       <c r="O21" s="21" t="s">
         <v>29</v>
       </c>
       <c r="P21" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q21" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="Q21" s="21" t="s">
+      <c r="R21" s="21" t="s">
         <v>136</v>
-      </c>
-      <c r="R21" s="21" t="s">
-        <v>137</v>
       </c>
       <c r="S21" s="22"/>
       <c r="V21" s="19"/>
@@ -3722,45 +6760,45 @@
     <row r="22" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="24"/>
       <c r="D22" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="F22" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="G22" s="26" t="s">
         <v>140</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>141</v>
       </c>
       <c r="H22" s="26"/>
       <c r="I22" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="J22" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="J22" s="26" t="s">
+      <c r="K22" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="L22" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="K22" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="L22" s="26" t="s">
+      <c r="M22" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="M22" s="26" t="s">
-        <v>145</v>
-      </c>
       <c r="N22" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O22" s="26"/>
       <c r="P22" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q22" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="Q22" s="26" t="s">
+      <c r="R22" s="26" t="s">
         <v>147</v>
-      </c>
-      <c r="R22" s="26" t="s">
-        <v>148</v>
       </c>
       <c r="S22" s="32"/>
       <c r="V22" s="19"/>
@@ -3772,7 +6810,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="G23" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
@@ -3783,7 +6821,7 @@
       <c r="N23" s="12"/>
       <c r="O23" s="12"/>
       <c r="P23" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
@@ -3792,45 +6830,45 @@
     <row r="24" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="16"/>
       <c r="D24" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E24" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="G24" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="G24" s="17" t="s">
-        <v>153</v>
-      </c>
       <c r="H24" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K24" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="L24" s="17" t="s">
         <v>154</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>155</v>
       </c>
       <c r="M24" s="17" t="s">
         <v>49</v>
       </c>
       <c r="N24" s="17"/>
       <c r="O24" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="P24" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="P24" s="17" t="s">
+      <c r="Q24" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="Q24" s="17" t="s">
-        <v>158</v>
-      </c>
       <c r="R24" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S24" s="18"/>
       <c r="V24" s="19"/>
@@ -3841,49 +6879,49 @@
         <v>6</v>
       </c>
       <c r="D25" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="E25" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="F25" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="F25" s="37" t="s">
+      <c r="G25" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="H25" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="I25" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="J25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="I25" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="J25" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="K25" s="21" t="s">
+      <c r="L25" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="L25" s="21" t="s">
+      <c r="M25" s="21" t="s">
         <v>165</v>
-      </c>
-      <c r="M25" s="21" t="s">
-        <v>166</v>
       </c>
       <c r="N25" s="21" t="s">
         <v>29</v>
       </c>
       <c r="O25" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="P25" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="P25" s="21" t="s">
+      <c r="Q25" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="Q25" s="21" t="s">
-        <v>169</v>
-      </c>
       <c r="R25" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S25" s="22"/>
       <c r="V25" s="19"/>
@@ -3891,45 +6929,45 @@
     <row r="26" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="24"/>
       <c r="D26" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="F26" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="G26" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="G26" s="26" t="s">
-        <v>173</v>
-      </c>
       <c r="H26" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I26" s="26"/>
       <c r="J26" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K26" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="L26" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="L26" s="26" t="s">
-        <v>175</v>
-      </c>
       <c r="M26" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N26" s="26"/>
       <c r="O26" s="26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P26" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q26" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="Q26" s="26" t="s">
-        <v>177</v>
-      </c>
       <c r="R26" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S26" s="32"/>
       <c r="V26" s="19"/>
@@ -3940,7 +6978,7 @@
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
@@ -3964,44 +7002,44 @@
       <c r="B28" s="16"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G28" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H28" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="H28" s="17" t="s">
+      <c r="I28" s="17" t="s">
         <v>181</v>
-      </c>
-      <c r="I28" s="17" t="s">
-        <v>182</v>
       </c>
       <c r="J28" s="17"/>
       <c r="K28" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="L28" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="L28" s="17" t="s">
+      <c r="M28" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="M28" s="17" t="s">
+      <c r="N28" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="N28" s="17" t="s">
+      <c r="O28" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="O28" s="17" t="s">
+      <c r="P28" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="P28" s="17" t="s">
+      <c r="Q28" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="Q28" s="17" t="s">
+      <c r="R28" s="17" t="s">
         <v>189</v>
-      </c>
-      <c r="R28" s="17" t="s">
-        <v>190</v>
       </c>
       <c r="S28" s="18"/>
       <c r="U28" s="35" t="str">
@@ -4019,46 +7057,46 @@
         <v>29</v>
       </c>
       <c r="E29" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="F29" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="G29" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="G29" s="21" t="s">
+      <c r="H29" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="H29" s="21" t="s">
+      <c r="I29" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="I29" s="21" t="s">
+      <c r="J29" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="J29" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="K29" s="21" t="s">
+      <c r="L29" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="L29" s="21" t="s">
+      <c r="M29" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="M29" s="21" t="s">
+      <c r="N29" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="N29" s="21" t="s">
+      <c r="O29" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="O29" s="21" t="s">
+      <c r="P29" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="P29" s="21" t="s">
+      <c r="Q29" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="Q29" s="21" t="s">
+      <c r="R29" s="21" t="s">
         <v>202</v>
-      </c>
-      <c r="R29" s="21" t="s">
-        <v>203</v>
       </c>
       <c r="S29" s="22"/>
       <c r="U29" s="35" t="str">
@@ -4071,44 +7109,44 @@
       <c r="B30" s="24"/>
       <c r="D30" s="26"/>
       <c r="E30" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="G30" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="H30" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="H30" s="26" t="s">
+      <c r="I30" s="26" t="s">
         <v>207</v>
-      </c>
-      <c r="I30" s="26" t="s">
-        <v>208</v>
       </c>
       <c r="J30" s="26"/>
       <c r="K30" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="L30" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="L30" s="26" t="s">
+      <c r="M30" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="M30" s="26" t="s">
+      <c r="N30" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="N30" s="26" t="s">
+      <c r="O30" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="O30" s="26" t="s">
+      <c r="P30" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="P30" s="26" t="s">
+      <c r="Q30" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="R30" s="26" t="s">
         <v>214</v>
-      </c>
-      <c r="Q30" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="R30" s="26" t="s">
-        <v>215</v>
       </c>
       <c r="S30" s="32"/>
       <c r="U30" s="35" t="str">
@@ -4121,11 +7159,11 @@
       <c r="B31" s="10"/>
       <c r="C31" s="36"/>
       <c r="D31" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
@@ -4135,12 +7173,12 @@
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
       <c r="N31" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O31" s="12"/>
       <c r="P31" s="12"/>
       <c r="Q31" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="R31" s="12"/>
       <c r="U31" s="35" t="str">
@@ -4152,45 +7190,45 @@
     <row r="32" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="16"/>
       <c r="D32" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>4</v>
       </c>
       <c r="K32" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="L32" s="17" t="s">
         <v>222</v>
-      </c>
-      <c r="L32" s="17" t="s">
-        <v>223</v>
       </c>
       <c r="M32" s="17"/>
       <c r="N32" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O32" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="P32" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="P32" s="17" t="s">
+      <c r="Q32" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="Q32" s="17" t="s">
+      <c r="R32" s="17" t="s">
         <v>226</v>
-      </c>
-      <c r="R32" s="17" t="s">
-        <v>227</v>
       </c>
       <c r="S32" s="18"/>
       <c r="U32" s="35" t="str">
@@ -4205,49 +7243,49 @@
         <v>8</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E33" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="G33" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="H33" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="H33" s="21" t="s">
-        <v>231</v>
-      </c>
       <c r="I33" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J33" s="21" t="s">
         <v>10</v>
       </c>
       <c r="K33" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="L33" s="21" t="s">
         <v>232</v>
-      </c>
-      <c r="L33" s="21" t="s">
-        <v>233</v>
       </c>
       <c r="M33" s="21" t="s">
         <v>29</v>
       </c>
       <c r="N33" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="O33" s="21" t="s">
         <v>234</v>
-      </c>
-      <c r="O33" s="21" t="s">
-        <v>235</v>
       </c>
       <c r="P33" s="21" t="s">
         <v>59</v>
       </c>
       <c r="Q33" s="21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R33" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S33" s="22"/>
       <c r="V33" s="19"/>
@@ -4255,45 +7293,45 @@
     <row r="34" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="24"/>
       <c r="D34" s="26" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E34" s="26"/>
       <c r="F34" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I34" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J34" s="26" t="s">
         <v>15</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L34" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M34" s="26"/>
       <c r="N34" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="O34" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="O34" s="26" t="s">
+      <c r="P34" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q34" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="P34" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q34" s="26" t="s">
+      <c r="R34" s="26" t="s">
         <v>242</v>
-      </c>
-      <c r="R34" s="26" t="s">
-        <v>243</v>
       </c>
       <c r="S34" s="32"/>
       <c r="V34" s="19"/>
@@ -4303,30 +7341,30 @@
       <c r="C35" s="36"/>
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J35" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="K35" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="K35" s="12" t="s">
+      <c r="L35" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="L35" s="12" t="s">
+      <c r="M35" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="M35" s="12" t="s">
+      <c r="N35" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="N35" s="12" t="s">
-        <v>249</v>
       </c>
       <c r="O35" s="12"/>
       <c r="P35" s="12"/>
@@ -4340,32 +7378,32 @@
         <v>5</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F36" s="17"/>
       <c r="G36" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="J36" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="H36" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="I36" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="J36" s="17" t="s">
+      <c r="K36" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="K36" s="17" t="s">
+      <c r="L36" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="L36" s="17" t="s">
+      <c r="M36" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="M36" s="17" t="s">
+      <c r="N36" s="17" t="s">
         <v>248</v>
-      </c>
-      <c r="N36" s="17" t="s">
-        <v>249</v>
       </c>
       <c r="O36" s="17"/>
       <c r="P36" s="17"/>
@@ -4383,37 +7421,37 @@
         <v>11</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F37" s="21" t="s">
         <v>29</v>
       </c>
       <c r="G37" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="I37" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="H37" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="I37" s="21" t="s">
+      <c r="J37" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="K37" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="L37" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="L37" s="21" t="s">
+      <c r="M37" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="N37" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="M37" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="N37" s="39" t="s">
-        <v>255</v>
-      </c>
       <c r="O37" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P37" s="21" t="str">
         <f>CHAR(10)</f>
@@ -4431,32 +7469,32 @@
         <v>16</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F38" s="26"/>
       <c r="G38" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="I38" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="J38" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="H38" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J38" s="26" t="s">
+      <c r="K38" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="K38" s="26" t="s">
+      <c r="L38" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="L38" s="26" t="s">
+      <c r="M38" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="N38" s="26" t="s">
         <v>259</v>
-      </c>
-      <c r="M38" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="N38" s="26" t="s">
-        <v>260</v>
       </c>
       <c r="O38" s="26"/>
       <c r="P38" s="26"/>
@@ -4471,18 +7509,18 @@
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
       <c r="F39" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
       <c r="K39" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L39" s="12"/>
       <c r="M39" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N39" s="12"/>
       <c r="O39" s="12"/>
@@ -4494,45 +7532,45 @@
     <row r="40" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="16"/>
       <c r="D40" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="E40" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="F40" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="G40" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="F40" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="G40" s="17" t="s">
+      <c r="H40" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="H40" s="17" t="s">
+      <c r="I40" s="17" t="s">
         <v>267</v>
-      </c>
-      <c r="I40" s="17" t="s">
-        <v>268</v>
       </c>
       <c r="J40" s="17"/>
       <c r="K40" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="L40" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="M40" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="L40" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="M40" s="17" t="s">
-        <v>263</v>
-      </c>
       <c r="N40" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O40" s="17" t="s">
         <v>4</v>
       </c>
       <c r="P40" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q40" s="17"/>
       <c r="R40" s="17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S40" s="18"/>
       <c r="V40" s="19"/>
@@ -4543,49 +7581,49 @@
         <v>10</v>
       </c>
       <c r="D41" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="E41" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="E41" s="21" t="s">
+      <c r="F41" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="F41" s="21" t="s">
+      <c r="G41" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="G41" s="21" t="s">
+      <c r="H41" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="H41" s="21" t="s">
+      <c r="I41" s="21" t="s">
         <v>275</v>
-      </c>
-      <c r="I41" s="21" t="s">
-        <v>276</v>
       </c>
       <c r="J41" s="21" t="s">
         <v>29</v>
       </c>
       <c r="K41" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="L41" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="L41" s="21" t="s">
+      <c r="M41" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="M41" s="21" t="s">
-        <v>279</v>
-      </c>
       <c r="N41" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O41" s="21" t="s">
         <v>10</v>
       </c>
       <c r="P41" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q41" s="21" t="s">
         <v>29</v>
       </c>
       <c r="R41" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="S41" s="22"/>
       <c r="V41" s="19"/>
@@ -4593,45 +7631,45 @@
     <row r="42" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="24"/>
       <c r="D42" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="E42" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="E42" s="26" t="s">
+      <c r="F42" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="G42" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="G42" s="26" t="s">
+      <c r="H42" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="H42" s="26" t="s">
+      <c r="I42" s="26" t="s">
         <v>286</v>
-      </c>
-      <c r="I42" s="26" t="s">
-        <v>287</v>
       </c>
       <c r="J42" s="26"/>
       <c r="K42" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L42" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N42" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O42" s="26" t="s">
         <v>15</v>
       </c>
       <c r="P42" s="26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q42" s="26"/>
       <c r="R42" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S42" s="32"/>
       <c r="V42" s="19"/>
@@ -4642,11 +7680,11 @@
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
       <c r="F43" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G43" s="12"/>
       <c r="H43" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12"/>
@@ -4654,14 +7692,14 @@
       <c r="L43" s="12"/>
       <c r="M43" s="12"/>
       <c r="N43" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O43" s="12" t="s">
         <v>40</v>
       </c>
       <c r="P43" s="12"/>
       <c r="Q43" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R43" s="12"/>
       <c r="V43" s="19"/>
@@ -4669,45 +7707,45 @@
     <row r="44" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="16"/>
       <c r="D44" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="E44" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="E44" s="17" t="s">
-        <v>295</v>
-      </c>
       <c r="F44" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G44" s="17"/>
       <c r="H44" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="L44" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="M44" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="N44" s="17" t="s">
         <v>291</v>
-      </c>
-      <c r="I44" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="J44" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="K44" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="L44" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="M44" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="N44" s="17" t="s">
-        <v>292</v>
       </c>
       <c r="O44" s="17" t="s">
         <v>40</v>
       </c>
       <c r="P44" s="17"/>
       <c r="Q44" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R44" s="17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S44" s="18"/>
       <c r="V44" s="19"/>
@@ -4718,49 +7756,49 @@
         <v>11</v>
       </c>
       <c r="D45" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="E45" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="F45" s="38" t="s">
         <v>302</v>
-      </c>
-      <c r="F45" s="38" t="s">
-        <v>303</v>
       </c>
       <c r="G45" s="21" t="s">
         <v>29</v>
       </c>
       <c r="H45" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="I45" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="I45" s="21" t="s">
+      <c r="J45" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="J45" s="21" t="s">
+      <c r="K45" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="K45" s="21" t="s">
+      <c r="L45" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="L45" s="21" t="s">
+      <c r="M45" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="N45" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="M45" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="N45" s="21" t="s">
+      <c r="O45" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="O45" s="21" t="s">
+      <c r="P45" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q45" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="P45" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q45" s="21" t="s">
+      <c r="R45" s="21" t="s">
         <v>311</v>
-      </c>
-      <c r="R45" s="21" t="s">
-        <v>312</v>
       </c>
       <c r="S45" s="22"/>
       <c r="V45" s="19"/>
@@ -4768,45 +7806,45 @@
     <row r="46" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="24"/>
       <c r="D46" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="E46" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E46" s="26" t="s">
+      <c r="F46" s="26" t="s">
         <v>314</v>
-      </c>
-      <c r="F46" s="26" t="s">
-        <v>315</v>
       </c>
       <c r="G46" s="26"/>
       <c r="H46" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="I46" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="J46" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="I46" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="J46" s="26" t="s">
+      <c r="K46" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="K46" s="26" t="s">
+      <c r="L46" s="26" t="s">
         <v>318</v>
       </c>
-      <c r="L46" s="26" t="s">
+      <c r="M46" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="N46" s="26" t="s">
         <v>319</v>
       </c>
-      <c r="M46" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="N46" s="26" t="s">
+      <c r="O46" s="26" t="s">
         <v>320</v>
-      </c>
-      <c r="O46" s="26" t="s">
-        <v>321</v>
       </c>
       <c r="P46" s="26"/>
       <c r="Q46" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="R46" s="26" t="s">
         <v>322</v>
-      </c>
-      <c r="R46" s="26" t="s">
-        <v>323</v>
       </c>
       <c r="S46" s="32"/>
       <c r="V46" s="19"/>
@@ -4821,7 +7859,7 @@
       <c r="H47" s="12"/>
       <c r="I47" s="12"/>
       <c r="J47" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K47" s="12"/>
       <c r="L47" s="12"/>
@@ -4836,23 +7874,23 @@
     <row r="48" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="16"/>
       <c r="D48" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="E48" s="17" t="s">
         <v>325</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>326</v>
       </c>
       <c r="F48" s="17"/>
       <c r="G48" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="H48" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="H48" s="17" t="s">
+      <c r="I48" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="I48" s="17" t="s">
-        <v>329</v>
-      </c>
       <c r="J48" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="17"/>
@@ -4871,28 +7909,28 @@
         <v>12</v>
       </c>
       <c r="D49" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E49" s="21" t="s">
         <v>330</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>331</v>
       </c>
       <c r="F49" s="21" t="s">
         <v>29</v>
       </c>
       <c r="G49" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="H49" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="H49" s="21" t="s">
+      <c r="I49" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="I49" s="21" t="s">
+      <c r="J49" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="J49" s="21" t="s">
-        <v>335</v>
-      </c>
       <c r="K49" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L49" s="21" t="str">
         <f>CHAR(10)</f>
@@ -4911,23 +7949,23 @@
     <row r="50" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="24"/>
       <c r="D50" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="E50" s="26" t="s">
         <v>336</v>
-      </c>
-      <c r="E50" s="26" t="s">
-        <v>337</v>
       </c>
       <c r="F50" s="26"/>
       <c r="G50" s="26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H50" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="I50" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="I50" s="26" t="s">
+      <c r="J50" s="26" t="s">
         <v>339</v>
-      </c>
-      <c r="J50" s="26" t="s">
-        <v>340</v>
       </c>
       <c r="K50" s="26"/>
       <c r="L50" s="26"/>
@@ -4965,11 +8003,11 @@
     <row r="52" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="16"/>
       <c r="D52" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E52" s="17"/>
       <c r="F52" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G52" s="17" t="s">
         <v>48</v>
@@ -4994,13 +8032,13 @@
         <v>13</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E53" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G53" s="38" t="s">
         <v>63</v>
@@ -5026,11 +8064,11 @@
     <row r="54" spans="2:22" s="2" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="24"/>
       <c r="D54" s="26" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E54" s="26"/>
       <c r="F54" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>48</v>
@@ -5095,7 +8133,7 @@
         <v>14</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E57" s="21"/>
       <c r="F57" s="21"/>
